--- a/solution_avec_planning.xlsx
+++ b/solution_avec_planning.xlsx
@@ -1012,7 +1012,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="hh:mm"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
